--- a/etf_holdings/2026-10-30_00981A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-30_00981A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-30 00:07:43</t>
+          <t>2026-10-30 23:07:46</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -524,16 +524,16 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>11.56%13,046,000</t>
+          <t>11.84%13,251,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>11.56%</t>
+          <t>11.84%</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>13046000</v>
+        <v>13251000</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -554,7 +554,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-30 00:07:43</t>
+          <t>2026-10-30 23:07:46</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -567,7 +567,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2383台光電</t>
+          <t>2454聯發科</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -587,16 +587,16 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>7.96%4,328,000</t>
+          <t>7.92%5,367,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>7.96%</t>
+          <t>7.92%</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>4328000</v>
+        <v>5367000</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -617,7 +617,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-30 00:07:43</t>
+          <t>2026-10-30 23:07:46</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -630,7 +630,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2454聯發科</t>
+          <t>3017奇鋐</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -650,16 +650,16 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>7.88%5,306,000</t>
+          <t>7.72%6,616,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>7.88%</t>
+          <t>7.72%</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>5306000</v>
+        <v>6616000</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -680,7 +680,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-30 00:07:43</t>
+          <t>2026-10-30 23:07:46</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3037欣興</t>
+          <t>2383台光電</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -713,16 +713,16 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>7.53%19,739,000</t>
+          <t>7.63%4,328,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>7.53%</t>
+          <t>7.63%</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>19739000</v>
+        <v>4328000</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -743,7 +743,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-30 00:07:43</t>
+          <t>2026-10-30 23:07:46</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>3017奇鋐</t>
+          <t>3037欣興</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -776,16 +776,16 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>7.45%6,537,000</t>
+          <t>7.36%19,739,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>7.45%</t>
+          <t>7.36%</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>6537000</v>
+        <v>19739000</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -806,7 +806,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-30 00:07:43</t>
+          <t>2026-10-30 23:07:46</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -839,12 +839,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5.91%2,512,000</t>
+          <t>5.98%2,512,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>5.91%</t>
+          <t>5.98%</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -869,7 +869,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-30 00:07:43</t>
+          <t>2026-10-30 23:07:46</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -902,12 +902,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>4.69%23,519,000</t>
+          <t>4.45%23,519,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>4.69%</t>
+          <t>4.45%</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -932,7 +932,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-30 00:07:43</t>
+          <t>2026-10-30 23:07:46</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -965,12 +965,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>4.45%2,504,000</t>
+          <t>4.35%2,504,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>4.45%</t>
+          <t>4.35%</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -995,7 +995,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-30 00:07:43</t>
+          <t>2026-10-30 23:07:46</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2308台達電</t>
+          <t>8046南電</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1028,16 +1028,16 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4.12%7,582,000</t>
+          <t>4.03%8,987,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>4.12%</t>
+          <t>4.03%</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>7582000</v>
+        <v>8987000</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -1058,7 +1058,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-30 00:07:43</t>
+          <t>2026-10-30 23:07:46</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>8046南電</t>
+          <t>2345智邦</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1091,16 +1091,16 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>4.12%8,987,000</t>
+          <t>3.86%6,331,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>4.12%</t>
+          <t>3.86%</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>8987000</v>
+        <v>6331000</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-30 00:07:43</t>
+          <t>2026-10-30 23:07:46</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2345智邦</t>
+          <t>2308台達電</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1154,16 +1154,16 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>4.08%6,331,000</t>
+          <t>3.82%7,582,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>4.08%</t>
+          <t>3.82%</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>6331000</v>
+        <v>7582000</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-30 00:07:43</t>
+          <t>2026-10-30 23:07:46</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3.70%7,262,000</t>
+          <t>3.46%7,262,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>3.70%</t>
+          <t>3.46%</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-30 00:07:43</t>
+          <t>2026-10-30 23:07:46</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1260,7 +1260,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2303聯電</t>
+          <t>3711日月光投控</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1280,16 +1280,16 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>3.38%79,618,000</t>
+          <t>3.42%13,588,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>3.38%</t>
+          <t>3.42%</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>79618000</v>
+        <v>13588000</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-30 00:07:43</t>
+          <t>2026-10-30 23:07:46</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2368金像電</t>
+          <t>2303聯電</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1343,16 +1343,16 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>3.13%7,636,000</t>
+          <t>3.35%79,618,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>3.13%</t>
+          <t>3.35%</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>7636000</v>
+        <v>79618000</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-30 00:07:43</t>
+          <t>2026-10-30 23:07:46</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>3711日月光投控</t>
+          <t>2368金像電</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1406,16 +1406,16 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.99%11,944,000</t>
+          <t>2.94%7,636,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2.99%</t>
+          <t>2.94%</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>11944000</v>
+        <v>7636000</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-30 00:07:47</t>
+          <t>2026-10-30 23:07:47</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1454,27 +1454,27 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-6.49%7640</t>
+          <t>-0.07%7635</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-6.49%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>7640</t>
+          <t>7635</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.59%923,000</t>
+          <t>2.66%923,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2.59%</t>
+          <t>2.66%</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-0.17%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-30 00:07:47</t>
+          <t>2026-10-30 23:07:47</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1517,27 +1517,27 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-3.33%1885</t>
+          <t>-3.98%1810</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-3.33%</t>
+          <t>-3.98%</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>1885</t>
+          <t>1810</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2.27%3,281,561</t>
+          <t>2.24%3,281,561</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2.27%</t>
+          <t>2.24%</t>
         </is>
       </c>
       <c r="K18" t="n">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-30 00:07:47</t>
+          <t>2026-10-30 23:07:47</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1580,27 +1580,27 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-5.8%1705</t>
+          <t>-4.69%1625</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-5.8%</t>
+          <t>-4.69%</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>1705</t>
+          <t>1625</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.81%2,887,848</t>
+          <t>1.77%2,887,848</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1.81%</t>
+          <t>1.77%</t>
         </is>
       </c>
       <c r="K19" t="n">
@@ -1608,7 +1608,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-0.11%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1625,7 +1625,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-30 00:07:47</t>
+          <t>2026-10-30 23:07:47</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1643,27 +1643,27 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-1.82%16980</t>
+          <t>-5.95%15970</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-1.82%</t>
+          <t>-5.95%</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>16980</t>
+          <t>15970</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.49%238,900</t>
+          <t>1.44%238,900</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.49%</t>
+          <t>1.44%</t>
         </is>
       </c>
       <c r="K20" t="n">
@@ -1671,7 +1671,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1688,7 +1688,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-30 00:07:47</t>
+          <t>2026-10-30 23:07:47</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1706,35 +1706,35 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-1.42%2425</t>
+          <t>-1.65%2385</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-1.42%</t>
+          <t>-1.65%</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2425</t>
+          <t>2385</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.07%1,206,000</t>
+          <t>1.27%1,412,000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1.07%</t>
+          <t>1.27%</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>1206000</v>
+        <v>1412000</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1751,7 +1751,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-30 00:07:47</t>
+          <t>2026-10-30 23:07:47</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1769,27 +1769,27 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-2.88%269.5</t>
+          <t>-5.94%253.5</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-2.88%</t>
+          <t>-5.94%</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>269.5</t>
+          <t>253.5</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.75%7,556,450</t>
+          <t>0.72%7,556,450</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.75%</t>
+          <t>0.72%</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -1797,7 +1797,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-30 00:07:47</t>
+          <t>2026-10-30 23:07:47</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1832,27 +1832,27 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-2.52%1545</t>
+          <t>-7.12%1435</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-2.52%</t>
+          <t>-7.12%</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>1545</t>
+          <t>1435</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.56%981,000</t>
+          <t>0.53%981,000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.56%</t>
+          <t>0.53%</t>
         </is>
       </c>
       <c r="K23" t="n">
@@ -1860,7 +1860,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1877,7 +1877,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-30 00:07:47</t>
+          <t>2026-10-30 23:07:47</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1895,17 +1895,17 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-10%2880</t>
+          <t>-2.08%2820</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-10%</t>
+          <t>-2.08%</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2880</t>
+          <t>2820</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1940,7 +1940,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-30 00:07:47</t>
+          <t>2026-10-30 23:07:47</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1958,27 +1958,27 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-0.42%236.5</t>
+          <t>-6.77%220.5</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-0.42%</t>
+          <t>-6.77%</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>236.5</t>
+          <t>220.5</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.44%5,027,000</t>
+          <t>0.42%5,027,000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.44%</t>
+          <t>0.42%</t>
         </is>
       </c>
       <c r="K25" t="n">
@@ -1986,7 +1986,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2003,7 +2003,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-30 00:07:47</t>
+          <t>2026-10-30 23:07:47</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2021,17 +2021,17 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-3.08%188.5</t>
+          <t>-2.65%183.5</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-3.08%</t>
+          <t>-2.65%</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>188.5</t>
+          <t>183.5</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-30 00:07:47</t>
+          <t>2026-10-30 23:07:47</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2084,27 +2084,27 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-3.96%206</t>
+          <t>-4.37%197</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-3.96%</t>
+          <t>-4.37%</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>197</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0.17%2,185,000</t>
+          <t>0.16%2,185,000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>0.17%</t>
+          <t>0.16%</t>
         </is>
       </c>
       <c r="K27" t="n">
@@ -2129,7 +2129,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-30 00:07:47</t>
+          <t>2026-10-30 23:07:47</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2147,27 +2147,27 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-2.35%477</t>
+          <t>-6.29%447</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-2.35%</t>
+          <t>-6.29%</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>477</t>
+          <t>447</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0.17%957,000</t>
+          <t>0.16%957,000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>0.17%</t>
+          <t>0.16%</t>
         </is>
       </c>
       <c r="K28" t="n">
@@ -2175,7 +2175,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-30 00:07:47</t>
+          <t>2026-10-30 23:07:47</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2210,17 +2210,17 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-7.06%84.3</t>
+          <t>-6.88%78.5</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-7.06%</t>
+          <t>-6.88%</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2255,7 +2255,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-30 00:07:47</t>
+          <t>2026-10-30 23:07:47</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2273,17 +2273,17 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-5.67%4655</t>
+          <t>-1.93%4565</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-5.67%</t>
+          <t>-1.93%</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>4655</t>
+          <t>4565</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2301,7 +2301,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2318,7 +2318,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-30 00:07:49</t>
+          <t>2026-10-30 23:07:51</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2336,25 +2336,25 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>-4.67%438.5</t>
+          <t>-7.64%405</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-4.67%</t>
+          <t>-7.64%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>438.5</v>
+        <v>405</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0.11%654,000</t>
+          <t>0.10%654,000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>0.11%</t>
+          <t>0.10%</t>
         </is>
       </c>
       <c r="K31" t="n">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-30 00:07:49</t>
+          <t>2026-10-30 23:07:51</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2397,25 +2397,25 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>-3.13%154.5</t>
+          <t>-9.71%139.5</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-3.13%</t>
+          <t>-9.71%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>154.5</v>
+        <v>139.5</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.10%1,740,000</t>
+          <t>0.09%1,740,000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.10%</t>
+          <t>0.09%</t>
         </is>
       </c>
       <c r="K32" t="n">
@@ -2423,7 +2423,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-30 00:07:49</t>
+          <t>2026-10-30 23:07:51</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2458,16 +2458,16 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>-3.2%756</t>
+          <t>-5.29%716</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-3.2%</t>
+          <t>-5.29%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>756</v>
+        <v>716</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -2501,7 +2501,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-30 00:07:49</t>
+          <t>2026-10-30 23:07:51</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2519,25 +2519,25 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-6.32%1260</t>
+          <t>-5.56%1190</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-6.32%</t>
+          <t>-5.56%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>1260</v>
+        <v>1190</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.06%121,000</t>
+          <t>0.05%121,000</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.06%</t>
+          <t>0.05%</t>
         </is>
       </c>
       <c r="K34" t="n">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-30 00:07:49</t>
+          <t>2026-10-30 23:07:51</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2580,16 +2580,16 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>-1.52%19.45</t>
+          <t>-1.03%19.25</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-1.52%</t>
+          <t>-1.03%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>19.45</v>
+        <v>19.25</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2623,7 +2623,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-30 00:07:49</t>
+          <t>2026-10-30 23:07:51</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2641,16 +2641,16 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-4.69%213.5</t>
+          <t>-5.39%202</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-4.69%</t>
+          <t>-5.39%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>213.5</v>
+        <v>202</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-30 00:07:49</t>
+          <t>2026-10-30 23:07:51</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2702,16 +2702,16 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>-3.68%275</t>
+          <t>-8.18%252.5</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-3.68%</t>
+          <t>-8.18%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>275</v>
+        <v>252.5</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2745,7 +2745,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-30 00:07:49</t>
+          <t>2026-10-30 23:07:51</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2763,16 +2763,16 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>-3.16%3680</t>
+          <t>-6.93%3425</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-3.16%</t>
+          <t>-6.93%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>3680</v>
+        <v>3425</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-30 00:07:49</t>
+          <t>2026-10-30 23:07:51</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2824,16 +2824,16 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>-1.37%79.3</t>
+          <t>-4.16%76</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-1.37%</t>
+          <t>-4.16%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>79.3</v>
+        <v>76</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-30 00:07:49</t>
+          <t>2026-10-30 23:07:51</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2885,16 +2885,16 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>+0.88%1150</t>
+          <t>-6.52%1075</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>+0.88%</t>
+          <t>-6.52%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>1150</v>
+        <v>1075</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-30 00:07:49</t>
+          <t>2026-10-30 23:07:51</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2946,16 +2946,16 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>-8.21%5815</t>
+          <t>-6.62%5430</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-8.21%</t>
+          <t>-6.62%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>5815</v>
+        <v>5430</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2989,7 +2989,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-30 00:07:49</t>
+          <t>2026-10-30 23:07:51</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3007,16 +3007,16 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>-5.45%520</t>
+          <t>-6.54%486</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-5.45%</t>
+          <t>-6.54%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>520</v>
+        <v>486</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -3050,7 +3050,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-30 00:07:49</t>
+          <t>2026-10-30 23:07:51</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3068,12 +3068,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>-3.64%318</t>
+          <t>0%318</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-3.64%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H43" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-30 00:07:49</t>
+          <t>2026-10-30 23:07:51</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3129,16 +3129,16 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>0%477</t>
+          <t>-4.72%454.5</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-4.72%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>477</v>
+        <v>454.5</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -3172,7 +3172,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-30 00:07:49</t>
+          <t>2026-10-30 23:07:51</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3190,16 +3190,16 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>+1.5%101.5</t>
+          <t>-0.99%100.5</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>+1.5%</t>
+          <t>-0.99%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>101.5</v>
+        <v>100.5</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -3233,7 +3233,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-30 00:07:50</t>
+          <t>2026-10-30 23:07:52</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3251,16 +3251,16 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>-4.42%1945</t>
+          <t>-9.77%1755</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-4.42%</t>
+          <t>-9.77%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>1945</v>
+        <v>1755</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -3294,7 +3294,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-30 00:07:50</t>
+          <t>2026-10-30 23:07:52</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3312,16 +3312,16 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>-4.12%814</t>
+          <t>-7.13%756</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-4.12%</t>
+          <t>-7.13%</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>814</v>
+        <v>756</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -3355,7 +3355,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-30 00:07:50</t>
+          <t>2026-10-30 23:07:52</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3373,16 +3373,16 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>-3.28%97.2</t>
+          <t>-6.48%90.9</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-3.28%</t>
+          <t>-6.48%</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>97.2</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -3416,7 +3416,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-30 00:07:50</t>
+          <t>2026-10-30 23:07:52</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3434,16 +3434,16 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>-1.39%248</t>
+          <t>-1.01%245.5</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-1.39%</t>
+          <t>-1.01%</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>248</v>
+        <v>245.5</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -3477,7 +3477,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-30 00:07:50</t>
+          <t>2026-10-30 23:07:52</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3495,16 +3495,16 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>-6.57%156.5</t>
+          <t>-7.99%144</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-6.57%</t>
+          <t>-7.99%</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>156.5</v>
+        <v>144</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -3538,7 +3538,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-30 00:07:50</t>
+          <t>2026-10-30 23:07:52</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3556,16 +3556,16 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>-4.5%148.5</t>
+          <t>-6.06%139.5</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-4.5%</t>
+          <t>-6.06%</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>148.5</v>
+        <v>139.5</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>

--- a/etf_holdings/2026-10-30_00981A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-30_00981A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-30 23:07:46</t>
+          <t>2026-10-30 23:18:45</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,18 +509,16 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-1.86%2370</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-1.86%</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>2370</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -537,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.22%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -554,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-30 23:07:46</t>
+          <t>2026-10-30 23:18:45</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -572,18 +570,16 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-3.21%3915</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-3.21%</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>3915</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -600,7 +596,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.25%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -617,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-30 23:07:46</t>
+          <t>2026-10-30 23:18:45</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -635,18 +631,16 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-0.32%3095</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-0.32%</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>3095</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -663,7 +657,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -680,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-30 23:07:46</t>
+          <t>2026-10-30 23:18:45</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -698,18 +692,16 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-6.69%4675</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-6.69%</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>4675</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -726,7 +718,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.52%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -743,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-30 23:07:46</t>
+          <t>2026-10-30 23:18:45</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -761,18 +753,16 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-4.9%989</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-4.9%</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>989</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -789,7 +779,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.36%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -806,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-30 23:07:46</t>
+          <t>2026-10-30 23:18:45</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -824,18 +814,16 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-1.41%6315</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-1.41%</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>6315</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -852,7 +840,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -869,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-30 23:07:46</t>
+          <t>2026-10-30 23:18:45</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -887,18 +875,16 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-7.55%502</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-7.55%</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>502</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -915,7 +901,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.35%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -932,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-30 23:07:46</t>
+          <t>2026-10-30 23:18:45</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -950,18 +936,16 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-4.75%4610</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-4.75%</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>4610</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -978,7 +962,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.21%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -995,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-30 23:07:46</t>
+          <t>2026-10-30 23:18:45</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1013,18 +997,16 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-4.8%1190</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-4.8%</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>1190</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1041,7 +1023,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.19%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1058,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-30 23:07:46</t>
+          <t>2026-10-30 23:18:45</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1076,18 +1058,16 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-7.98%1615</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-7.98%</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>1615</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1104,7 +1084,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.32%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1121,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-30 23:07:46</t>
+          <t>2026-10-30 23:18:45</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1139,18 +1119,16 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-9.8%1335</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-9.8%</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>1335</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1167,7 +1145,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.40%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1184,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-30 23:07:46</t>
+          <t>2026-10-30 23:18:45</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1202,18 +1180,16 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-8.99%1265</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-8.99%</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>1265</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1230,7 +1206,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.33%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1247,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-30 23:07:46</t>
+          <t>2026-10-30 23:18:45</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1265,18 +1241,16 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-2.2%668</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-2.2%</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>668</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1293,7 +1267,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1310,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-30 23:07:46</t>
+          <t>2026-10-30 23:18:45</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1328,18 +1302,16 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-3.46%111.5</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-3.46%</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>111.5</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1356,7 +1328,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.12%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1373,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-30 23:07:46</t>
+          <t>2026-10-30 23:18:45</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1391,18 +1363,16 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-8.52%1020</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-8.52%</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>1020</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1419,7 +1389,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.26%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1436,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-30 23:07:47</t>
+          <t>2026-10-30 23:18:46</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1499,7 +1469,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-30 23:07:47</t>
+          <t>2026-10-30 23:18:46</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1562,7 +1532,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-30 23:07:47</t>
+          <t>2026-10-30 23:18:46</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1625,7 +1595,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-30 23:07:47</t>
+          <t>2026-10-30 23:18:46</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1688,7 +1658,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-30 23:07:47</t>
+          <t>2026-10-30 23:18:46</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1751,7 +1721,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-30 23:07:47</t>
+          <t>2026-10-30 23:18:46</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1814,7 +1784,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-30 23:07:47</t>
+          <t>2026-10-30 23:18:46</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1877,7 +1847,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-30 23:07:47</t>
+          <t>2026-10-30 23:18:46</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1940,7 +1910,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-30 23:07:47</t>
+          <t>2026-10-30 23:18:46</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2003,7 +1973,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-30 23:07:47</t>
+          <t>2026-10-30 23:18:46</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2066,7 +2036,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-30 23:07:47</t>
+          <t>2026-10-30 23:18:46</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2129,7 +2099,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-30 23:07:47</t>
+          <t>2026-10-30 23:18:46</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2192,7 +2162,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-30 23:07:47</t>
+          <t>2026-10-30 23:18:46</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2255,7 +2225,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-30 23:07:47</t>
+          <t>2026-10-30 23:18:46</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2318,7 +2288,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-30 23:07:51</t>
+          <t>2026-10-30 23:18:48</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2379,7 +2349,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-30 23:07:51</t>
+          <t>2026-10-30 23:18:48</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2440,7 +2410,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-30 23:07:51</t>
+          <t>2026-10-30 23:18:48</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2501,7 +2471,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-30 23:07:51</t>
+          <t>2026-10-30 23:18:48</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2562,7 +2532,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-30 23:07:51</t>
+          <t>2026-10-30 23:18:48</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2623,7 +2593,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-30 23:07:51</t>
+          <t>2026-10-30 23:18:48</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2684,7 +2654,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-30 23:07:51</t>
+          <t>2026-10-30 23:18:48</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2745,7 +2715,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-30 23:07:51</t>
+          <t>2026-10-30 23:18:48</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2806,7 +2776,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-30 23:07:51</t>
+          <t>2026-10-30 23:18:48</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2867,7 +2837,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-30 23:07:51</t>
+          <t>2026-10-30 23:18:48</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2928,7 +2898,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-30 23:07:51</t>
+          <t>2026-10-30 23:18:48</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2989,7 +2959,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-30 23:07:51</t>
+          <t>2026-10-30 23:18:48</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3050,7 +3020,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-30 23:07:51</t>
+          <t>2026-10-30 23:18:48</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3111,7 +3081,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-30 23:07:51</t>
+          <t>2026-10-30 23:18:48</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3172,7 +3142,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-30 23:07:51</t>
+          <t>2026-10-30 23:18:48</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3233,7 +3203,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-30 23:07:52</t>
+          <t>2026-10-30 23:18:49</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3294,7 +3264,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-30 23:07:52</t>
+          <t>2026-10-30 23:18:49</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3355,7 +3325,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-30 23:07:52</t>
+          <t>2026-10-30 23:18:49</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3416,7 +3386,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-30 23:07:52</t>
+          <t>2026-10-30 23:18:49</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3477,7 +3447,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-30 23:07:52</t>
+          <t>2026-10-30 23:18:49</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3538,7 +3508,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-30 23:07:52</t>
+          <t>2026-10-30 23:18:49</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-10-30_00981A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-30_00981A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-30 23:18:45</t>
+          <t>2026-10-30 23:55:45</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-30 23:18:45</t>
+          <t>2026-10-30 23:55:45</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-30 23:18:45</t>
+          <t>2026-10-30 23:55:45</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-30 23:18:45</t>
+          <t>2026-10-30 23:55:45</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-30 23:18:45</t>
+          <t>2026-10-30 23:55:45</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-30 23:18:45</t>
+          <t>2026-10-30 23:55:45</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-30 23:18:45</t>
+          <t>2026-10-30 23:55:45</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-30 23:18:45</t>
+          <t>2026-10-30 23:55:45</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-30 23:18:45</t>
+          <t>2026-10-30 23:55:45</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-30 23:18:45</t>
+          <t>2026-10-30 23:55:45</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-30 23:18:45</t>
+          <t>2026-10-30 23:55:45</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-30 23:18:45</t>
+          <t>2026-10-30 23:55:45</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-30 23:18:45</t>
+          <t>2026-10-30 23:55:45</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-30 23:18:45</t>
+          <t>2026-10-30 23:55:45</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-30 23:18:45</t>
+          <t>2026-10-30 23:55:45</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-30 23:18:46</t>
+          <t>2026-10-30 23:55:46</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-30 23:18:46</t>
+          <t>2026-10-30 23:55:46</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-30 23:18:46</t>
+          <t>2026-10-30 23:55:46</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-30 23:18:46</t>
+          <t>2026-10-30 23:55:46</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-30 23:18:46</t>
+          <t>2026-10-30 23:55:46</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-30 23:18:46</t>
+          <t>2026-10-30 23:55:46</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1784,7 +1784,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-30 23:18:46</t>
+          <t>2026-10-30 23:55:46</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-30 23:18:46</t>
+          <t>2026-10-30 23:55:46</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-30 23:18:46</t>
+          <t>2026-10-30 23:55:46</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-30 23:18:46</t>
+          <t>2026-10-30 23:55:46</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-30 23:18:46</t>
+          <t>2026-10-30 23:55:46</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-30 23:18:46</t>
+          <t>2026-10-30 23:55:46</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-30 23:18:46</t>
+          <t>2026-10-30 23:55:46</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-30 23:18:46</t>
+          <t>2026-10-30 23:55:46</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-30 23:18:48</t>
+          <t>2026-10-30 23:55:47</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2349,7 +2349,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-30 23:18:48</t>
+          <t>2026-10-30 23:55:47</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-30 23:18:48</t>
+          <t>2026-10-30 23:55:47</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-30 23:18:48</t>
+          <t>2026-10-30 23:55:47</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-30 23:18:48</t>
+          <t>2026-10-30 23:55:47</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-30 23:18:48</t>
+          <t>2026-10-30 23:55:47</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2654,7 +2654,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-30 23:18:48</t>
+          <t>2026-10-30 23:55:47</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-30 23:18:48</t>
+          <t>2026-10-30 23:55:47</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-30 23:18:48</t>
+          <t>2026-10-30 23:55:47</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2837,7 +2837,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-30 23:18:48</t>
+          <t>2026-10-30 23:55:47</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-30 23:18:48</t>
+          <t>2026-10-30 23:55:47</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-30 23:18:48</t>
+          <t>2026-10-30 23:55:47</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-30 23:18:48</t>
+          <t>2026-10-30 23:55:47</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-30 23:18:48</t>
+          <t>2026-10-30 23:55:47</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-30 23:18:48</t>
+          <t>2026-10-30 23:55:47</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3203,7 +3203,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-30 23:18:49</t>
+          <t>2026-10-30 23:55:49</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-30 23:18:49</t>
+          <t>2026-10-30 23:55:49</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-30 23:18:49</t>
+          <t>2026-10-30 23:55:49</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-30 23:18:49</t>
+          <t>2026-10-30 23:55:49</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3447,7 +3447,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-30 23:18:49</t>
+          <t>2026-10-30 23:55:49</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-30 23:18:49</t>
+          <t>2026-10-30 23:55:49</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
